--- a/datos/Semana29.xlsx
+++ b/datos/Semana29.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
   <si>
     <t>Planificación semanal</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>LUCES DE BODEGA DE ALIMENTO Y BICARBONATO EN MAL ESTADO</t>
-  </si>
-  <si>
-    <t>Asistentes de mantención</t>
   </si>
   <si>
     <t>CAMBIO DE FLUORESCENTES EN MAL ESTADO</t>
@@ -226,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -257,19 +254,6 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -277,11 +261,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -312,13 +293,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -611,518 +592,518 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
+      <c r="A3" s="2">
         <v>46216</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>10033543</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>20018680</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="6" t="s">
+      <c r="E3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="7">
+      <c r="A4" s="6">
         <v>46216</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>10033543</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>20018680</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="9"/>
+      <c r="G4" s="8"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="7">
+      <c r="A5" s="6">
         <v>46216</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>10032774</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>20017109</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="7">
+      <c r="A6" s="6">
         <v>46216</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="3">
         <v>10032367</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>20017561</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="7">
+      <c r="A7" s="6">
         <v>46216</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="3">
         <v>10032368</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="3">
         <v>20017562</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="7">
+      <c r="A8" s="6">
         <v>46217</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="3">
         <v>10033512</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="3">
         <v>20018582</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="8"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
+      <c r="A9" s="6">
         <v>46217</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="3">
         <v>10033513</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="3">
         <v>20018681</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="E9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="8"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="7">
+      <c r="A10" s="6">
         <v>46217</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="3">
         <v>10032371</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="3">
         <v>20017318</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="7">
+      <c r="A11" s="6">
         <v>46217</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>10032369</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="9">
         <v>20017568</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="7">
+      <c r="A12" s="6">
         <v>46217</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>10032446</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="9">
         <v>20014753</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="7">
+      <c r="A13" s="6">
         <v>46218</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>10033543</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="3">
         <v>20018680</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="8"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="7">
+      <c r="A14" s="6">
         <v>46218</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>10033537</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="10">
         <v>10033537</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="E14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="7">
+      <c r="A15" s="6">
         <v>46218</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>10032370</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>20017320</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="7">
+      <c r="A16" s="6">
         <v>46219</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="3">
         <v>10032686</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="3">
         <v>10012563</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" s="9" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B17" s="7">
+        <v>10033653</v>
+      </c>
+      <c r="C17" s="10">
+        <v>20018625</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="7">
-        <v>46219</v>
-      </c>
-      <c r="B17" s="8">
-        <v>10033653</v>
-      </c>
-      <c r="C17" s="11">
-        <v>20018625</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B18" s="7">
+        <v>10033353</v>
+      </c>
+      <c r="C18" s="10">
+        <v>20018461</v>
+      </c>
+      <c r="D18" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="7">
+      <c r="E18" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="6">
         <v>46220</v>
       </c>
-      <c r="B18" s="8">
-        <v>10033353</v>
-      </c>
-      <c r="C18" s="11">
-        <v>20018461</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="B19" s="7">
+        <v>10033545</v>
+      </c>
+      <c r="C19" s="7">
+        <v>20018683</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="7">
+      <c r="G19" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="6">
         <v>46220</v>
       </c>
-      <c r="B19" s="8">
-        <v>10033545</v>
-      </c>
-      <c r="C19" s="8">
-        <v>20018683</v>
-      </c>
-      <c r="D19" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="13" t="s">
+      <c r="B20" s="7">
+        <v>10032275</v>
+      </c>
+      <c r="C20" s="10">
+        <v>20017321</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="7">
+      <c r="E20" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="6">
         <v>46220</v>
       </c>
-      <c r="B20" s="8">
-        <v>10032275</v>
-      </c>
-      <c r="C20" s="11">
-        <v>20017321</v>
-      </c>
-      <c r="D20" s="6" t="s">
+      <c r="B21" s="7">
+        <v>10033546</v>
+      </c>
+      <c r="C21" s="10">
+        <v>20018684</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="7">
+      <c r="E21" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22" s="6">
         <v>46220</v>
       </c>
-      <c r="B21" s="8">
-        <v>10033546</v>
-      </c>
-      <c r="C21" s="11">
-        <v>20018684</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="9" t="s">
+      <c r="B22" s="7">
+        <v>10032370</v>
+      </c>
+      <c r="C22" s="10">
+        <v>20017320</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23" s="6">
+        <v>46221</v>
+      </c>
+      <c r="B23" s="7">
+        <v>10033547</v>
+      </c>
+      <c r="C23" s="10">
+        <v>10013077</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="7">
-        <v>46220</v>
-      </c>
-      <c r="B22" s="8">
-        <v>10032370</v>
-      </c>
-      <c r="C22" s="11">
-        <v>20017320</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
+      <c r="E23" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
         <v>46221</v>
       </c>
-      <c r="B23" s="8">
-        <v>10033547</v>
-      </c>
-      <c r="C23" s="11">
-        <v>10013077</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G23" s="9" t="s">
+      <c r="B24" s="7">
+        <v>10033548</v>
+      </c>
+      <c r="C24" s="10">
+        <v>20018642</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A24" s="7">
-        <v>46221</v>
-      </c>
-      <c r="B24" s="8">
-        <v>10033548</v>
-      </c>
-      <c r="C24" s="11">
-        <v>20018642</v>
-      </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="9" t="s">
+      <c r="G24" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="9" t="s">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
+        <v>46222</v>
+      </c>
+      <c r="B25" s="7">
+        <v>10033550</v>
+      </c>
+      <c r="C25" s="7">
+        <v>20018685</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A25" s="7">
-        <v>46222</v>
-      </c>
-      <c r="B25" s="8">
-        <v>10033550</v>
-      </c>
-      <c r="C25" s="8">
-        <v>20018685</v>
-      </c>
-      <c r="D25" s="9" t="s">
+      <c r="E25" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/datos/Semana29.xlsx
+++ b/datos/Semana29.xlsx
@@ -852,7 +852,7 @@
         <v>10033537</v>
       </c>
       <c r="C14" s="10">
-        <v>10033537</v>
+        <v>20018641</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>27</v>
@@ -951,7 +951,7 @@
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="1:7" ht="37" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="6">
         <v>46220</v>
       </c>
